--- a/docs/sed-requisitos-wbs.xlsx
+++ b/docs/sed-requisitos-wbs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Frankil Aldair Perez\Documents\Code\sed-evaluacion-desempeno\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE5A8B3-CB68-4404-97D5-4053A45524F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879C3981-F974-4C97-99BC-E740AF4A3971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Solicitud de Requisitos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="283">
   <si>
     <t>SED — Solicitud de Requisitos</t>
   </si>
@@ -53,7 +53,7 @@
     <t>Pantalla Principal</t>
   </si>
   <si>
-    <t>Todos los usuarios</t>
+    <t>Todos</t>
   </si>
   <si>
     <t>Un sistema con menú lateral para navegar entre módulos</t>
@@ -131,22 +131,22 @@
     <t>Organizar metas relacionadas</t>
   </si>
   <si>
-    <t>Se pueden crear, ver, editar y eliminar categorías. Son independientes de las competencias</t>
+    <t>La lista muestra: Nombre de la categoría, Descripción, Peso y Acciones (editar, eliminar). Son independientes de las competencias</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>Registrar metas con nombre, descripción, unidad, valor esperado y peso</t>
-  </si>
-  <si>
-    <t>Formulario para agregar metas dentro de cada categoría</t>
-  </si>
-  <si>
-    <t>Definir indicadores concretos por categoría</t>
-  </si>
-  <si>
-    <t>La unidad puede ser porcentaje (%) o moneda ($). El peso de todas las metas de una categoría suma 100%</t>
+    <t>Registrar metas con nombre, descripción, unidad, valor objetivo, peso y comportamiento</t>
+  </si>
+  <si>
+    <t>Formulario para agregar metas dentro de cada categoría. Cada meta puede ser hacia arriba (más es mejor) o hacia abajo (menos es mejor)</t>
+  </si>
+  <si>
+    <t>Definir indicadores y metas concretos por categoría</t>
+  </si>
+  <si>
+    <t>La unidad puede ser porcentaje (%), moneda ($) o numérico (#). El peso de todas las metas de una categoría suma 100%. Se visualiza una tabla con: Meta, Valor objetivo, Peso, KPI asociado y Acciones (editar, eliminar)</t>
   </si>
   <si>
     <t>7</t>
@@ -158,13 +158,13 @@
     <t>Que se valide que los porcentajes siempre sumen 100</t>
   </si>
   <si>
-    <t>Indicador visual que muestra el progreso y no deja guardar si no cuadra</t>
+    <t>Indicador visual que muestra el progreso y no deja guardar si no suma 100%</t>
   </si>
   <si>
     <t>Asegurar que las ponderaciones sean correctas</t>
   </si>
   <si>
-    <t>Cada categoría suma 100%. Las metas dentro de cada categoría suman 100%. No se puede guardar si hay error</t>
+    <t>Cada categoría suma 100% global. Las metas dentro de cada categoría suman 100%. No se puede guardar si hay error</t>
   </si>
   <si>
     <t>8</t>
@@ -182,7 +182,7 @@
     <t>Supervisión sin riesgo de borrado accidental</t>
   </si>
   <si>
-    <t>El jefe no puede borrar ni agregar metas. Solo solicitar cambios. El dueño decide si acepta</t>
+    <t>El jefe no puede borrar ni agregar metas. Al pedir cambios se abre una caja de comentarios tipo chat entre el jefe directo y el empleado, que puede ser sobre una meta individual o sobre todas las metas del empleado. El jefe escribe su observación, el empleado la ve, responde y al final decide si acepta o rechaza el cambio solicitado</t>
   </si>
   <si>
     <t>9</t>
@@ -191,13 +191,13 @@
     <t>Un catálogo de indicadores predefinidos para reusar</t>
   </si>
   <si>
-    <t>Pantalla con lista de indicadores que se pueden asignar a las metas</t>
-  </si>
-  <si>
-    <t>Tener indicadores estándar reutilizables</t>
-  </si>
-  <si>
-    <t>Los indicadores pueden ser numéricos, porcentaje o moneda. Se vinculan a una o más metas</t>
+    <t>Pantalla con lista de indicadores. Cada indicador puede ser hacia arriba (más es mejor) o hacia abajo (menos es mejor)</t>
+  </si>
+  <si>
+    <t>Tener indicadores estándar medibles y reutilizables</t>
+  </si>
+  <si>
+    <t>Los indicadores pueden ser numéricos, porcentaje o moneda. Se vinculan a una o más metas. Se visualiza Nombre, Descripción, Unidad, Objetivo</t>
   </si>
   <si>
     <t>10</t>
@@ -212,7 +212,7 @@
     <t>Gestión centralizada de las metas del equipo</t>
   </si>
   <si>
-    <t>El selector marca "(Yo)" para el usuario actual. Usa el organigrama de la empresa</t>
+    <t>El selector marca "(Yo)" para el usuario actual. Usa el organigrama de la empresa para empleados a cargo.</t>
   </si>
   <si>
     <t>11</t>
@@ -236,22 +236,22 @@
     <t>Metas — Avance de Medio Año</t>
   </si>
   <si>
-    <t>actualizar mis metas existentes en la fase de medio año</t>
-  </si>
-  <si>
-    <t>Pantalla donde se ajustan los campos permitidos de las metas</t>
-  </si>
-  <si>
-    <t>Registrar cambios de mitad de año</t>
-  </si>
-  <si>
-    <t>No se pueden eliminar metas. Solo se ajustan los valores permitidos</t>
+    <t>Comentar avance de metas existentes en la fase de medio año</t>
+  </si>
+  <si>
+    <t>Botón de comentarios con pantalla tipo chat entre el jefe directo y el empleado</t>
+  </si>
+  <si>
+    <t>Registrar retroalimentación para mejorar a mitad de año</t>
+  </si>
+  <si>
+    <t>No se pueden eliminar metas. Permite ver todos los comentarios.</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
-    <t>registrar el avance de cada meta</t>
+    <t>Registrar el avance de cada meta</t>
   </si>
   <si>
     <t>Formulario para ingresar avance con barra visual de progreso</t>
@@ -269,7 +269,7 @@
     <t>Mi Evaluación — Autoevaluación de Fin de Año</t>
   </si>
   <si>
-    <t>autoevaluar mis competencias con escala del 1 al 5</t>
+    <t>Autoevaluar mis competencias con escala del 1 al 5</t>
   </si>
   <si>
     <t>Pantalla con tarjetas de competencias y selector de puntaje</t>
@@ -278,13 +278,13 @@
     <t>Que cada empleado evalúe sus propias competencias</t>
   </si>
   <si>
-    <t>Escala 1 a 5 con descripciones según el perfil del empleado</t>
+    <t>Cada tarjeta muestra: nombre de la competencia, puntaje seleccionado (1-5), y espacio de comentarios</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
-    <t>ver un gráfico de radar con mis resultados de competencias</t>
+    <t>Ver un gráfico de radar con mis resultados de competencias</t>
   </si>
   <si>
     <t>Visualización en forma de gráfico o tabla intercambiable</t>
@@ -293,13 +293,13 @@
     <t>Ver fortalezas y debilidades de forma visual</t>
   </si>
   <si>
-    <t>Se puede cambiar entre gráfico y tabla. Los colores se adaptan al tema claro/oscuro</t>
+    <t>La tabla muestra: Competencia, Puntaje, Mínimo esperado, Diferencia. Se puede cambiar entre gráfico y tabla. Los colores se adaptan al tema claro/oscuro</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
-    <t>cerrar mis metas al final del ciclo</t>
+    <t>Cerrar mis metas al final del ciclo</t>
   </si>
   <si>
     <t>Pantalla para registrar el cumplimiento final de cada meta</t>
@@ -308,7 +308,7 @@
     <t>Formalizar el resultado de cada meta al cierre del año</t>
   </si>
   <si>
-    <t>Se registra valor final y comentarios por meta</t>
+    <t>Para cada meta se muestra: nombre, objetivo, KPIs, comentarios y avance final. Al cerrar el ciclo se bloquea la edición</t>
   </si>
   <si>
     <t>17</t>
@@ -317,7 +317,7 @@
     <t>Jefe / RH</t>
   </si>
   <si>
-    <t>descargar la evaluación de empleados en archivo</t>
+    <t>Descargar la evaluación de empleados en archivo</t>
   </si>
   <si>
     <t>Botón "Descargar" que genera un archivo con los datos de la tabla</t>
@@ -338,7 +338,7 @@
     <t>RH</t>
   </si>
   <si>
-    <t>administrar pilares (categorías de competencias)</t>
+    <t>Administrar pilares (categorías de competencias)</t>
   </si>
   <si>
     <t>Pantalla para crear, ver, editar y eliminar pilares</t>
@@ -347,13 +347,13 @@
     <t>Mantener el catálogo de pilares de competencias de la empresa</t>
   </si>
   <si>
-    <t>Listado con opciones de crear, editar y eliminar con confirmación</t>
+    <t>La lista muestra: Nombre del pilar, Descripción, Acciones (editar, eliminar con confirmación)</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>administrar competencias dentro de cada pilar</t>
+    <t>Administrar competencias dentro de cada pilar</t>
   </si>
   <si>
     <t>Pantalla para crear, ver, editar y eliminar competencias</t>
@@ -362,28 +362,28 @@
     <t>Definir las competencias específicas por pilar</t>
   </si>
   <si>
-    <t>Cada competencia pertenece a un solo pilar. Se puede crear, editar y eliminar</t>
+    <t>La lista muestra: Nombre de la competencia, Pilar al que pertenece, Descripción, Acciones (editar, eliminar)</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>definir qué significa cada nivel de calificación por competencia</t>
-  </si>
-  <si>
-    <t>Pantalla para establecer criterios del 1 al 5 por competencia y perfil</t>
+    <t>Definir qué significa cada nivel de calificación por competencia</t>
+  </si>
+  <si>
+    <t>Pantalla para establecer criterios del 1 al 5 por competencia y nivel</t>
   </si>
   <si>
     <t>Estandarizar la evaluación con descripciones claras de cada nivel</t>
   </si>
   <si>
-    <t>Escala fija 1 a 5. Los criterios cambian según el perfil del puesto</t>
+    <t>Escala fija 1 a 5. Los criterios cambian según el nivel esperado</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>definir el puntaje mínimo requerido por competencia</t>
+    <t>Definir el puntaje mínimo requerido por perfil y competencia</t>
   </si>
   <si>
     <t>Pantalla para establecer niveles de aceptación por perfil</t>
@@ -392,7 +392,7 @@
     <t>Saber si un empleado cumple el mínimo esperado en cada competencia</t>
   </si>
   <si>
-    <t>Cada perfil tiene sus propios niveles mínimos</t>
+    <t>Por cada perfil se muestra: Competencia, Puntaje mínimo aceptado. Se muestra cuadro comparativo entre perfiles por competencia</t>
   </si>
   <si>
     <t>22</t>
@@ -401,7 +401,7 @@
     <t>Evaluación RH — Fin de Año</t>
   </si>
   <si>
-    <t>ver una lista de empleados con estado de su evaluación</t>
+    <t>Ver una lista de empleados con estado de su evaluación</t>
   </si>
   <si>
     <t>Pantalla con tabla de empleados y su estado actual</t>
@@ -410,22 +410,22 @@
     <t>Que RH dé seguimiento a las evaluaciones pendientes</t>
   </si>
   <si>
-    <t>Estados: pendiente, en progreso, completada</t>
+    <t>La tabla muestra: Nombre del empleado, Perfil, Estado de evaluación (pendiente, en progreso, completada), Acciones (evaluar)</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>comparar la autoevaluación del empleado con la evaluación de RH</t>
-  </si>
-  <si>
-    <t>Pantalla que muestra lado a lado ambas calificaciones</t>
+    <t>Comparar la autoevaluación del empleado y realizar evaluación de RH</t>
+  </si>
+  <si>
+    <t>Pantalla que muestra resumen de calificaciones, metas y competencias de empleados.</t>
   </si>
   <si>
     <t>Detectar diferencias entre cómo se ve el empleado y cómo lo ve RH</t>
   </si>
   <si>
-    <t>Vista lado a lado de las calificaciones de ambas partes</t>
+    <t>Por cada competencia se muestra: Autoevaluación del empleado, Evaluación de RH, Diferencia entre ambas. Por cada meta se permite agregar comentarios. Por cada competencia se permite evaluar en escala 1-5 y agregar comentarios.</t>
   </si>
   <si>
     <t>24</t>
@@ -434,22 +434,22 @@
     <t>Matriz 9×9 — Evaluación de Jefes</t>
   </si>
   <si>
-    <t>ubicar a mis colaboradores en una cuadrícula de desempeño versus potencial</t>
-  </si>
-  <si>
-    <t>Cuadrícula interactiva para posicionar a cada empleado</t>
+    <t>Ubicar a mis colaboradores en una cuadrícula de desempeño contra potencial</t>
+  </si>
+  <si>
+    <t>Cuadrícula interactiva para visualizar a cada empleado</t>
   </si>
   <si>
     <t>Visualizar el talento del equipo en un solo vistazo</t>
   </si>
   <si>
-    <t>La cuadrícula se puede usar interactivamente. No reemplaza la evaluación de competencias</t>
+    <t>La cuadrícula se puede usar interactivamente. No reemplaza la evaluación de competencias.</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>navegar el organigrama de la empresa</t>
+    <t>Navegar el organigrama de la empresa</t>
   </si>
   <si>
     <t>Árbol visual para explorar la jerarquía organizacional</t>
@@ -458,13 +458,13 @@
     <t>Navegar entre colaboradores según su posición en la empresa</t>
   </si>
   <si>
-    <t>Dos vistas disponibles: corporativa y retail</t>
+    <t>Vistas disponibles: vista de Directores (muestra el equipo a cargo) y vista de RH (muestra toda la empresa con el promedio de evaluación por área). Al seleccionar una persona del árbol se muestra: nombre, cargo, perfil, promedio de evaluación y personas a cargo</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>consultar las competencias de mis colaboradores</t>
+    <t>Consultar las competencias de mis colaboradores</t>
   </si>
   <si>
     <t>Pantalla donde el jefe ve las competencias de sus subordinados</t>
@@ -473,9 +473,6 @@
     <t>Que el jefe conozca las evaluaciones de su equipo</t>
   </si>
   <si>
-    <t>El jefe puede ver pero no calificar (esa tarea es de RH)</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -485,7 +482,7 @@
     <t>Jefe / Director</t>
   </si>
   <si>
-    <t>ver la lista de mis colaboradores directos</t>
+    <t>Ver la lista de mis colaboradores directos</t>
   </si>
   <si>
     <t>Pantalla con lista de personas a cargo</t>
@@ -494,564 +491,372 @@
     <t>Acceso rápido a metas y evaluaciones del equipo</t>
   </si>
   <si>
-    <t>El jefe ve sus reportes directos, un director ve toda su área</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>La lista muestra: Nombre, Cargo, Perfil, Estado de evaluación, Acción (evaluar). El jefe ve sus empleados directos, un director ve toda su área. Puede agregar comentarios por meta.</t>
   </si>
   <si>
     <t>Perfil de Usuario</t>
   </si>
   <si>
-    <t>ver mi página de perfil con datos personales y actividad reciente</t>
-  </si>
-  <si>
-    <t>Pantalla con nombre, correo, inicial del usuario e historial de actividad</t>
-  </si>
-  <si>
-    <t>Ver la identidad del usuario y su actividad en el sistema</t>
-  </si>
-  <si>
-    <t>Muestra datos del usuario, botón para cerrar sesión y actividad filtrada por perfil</t>
-  </si>
-  <si>
-    <t>Lista maestra de requisitos</t>
-  </si>
-  <si>
-    <t>Infraestructura del Sistema</t>
-  </si>
-  <si>
-    <t>Fuente principal de los 33 requerimientos</t>
-  </si>
-  <si>
-    <t>Sistema de comentarios por requisito</t>
-  </si>
-  <si>
-    <t>Notas y comentarios en cada requerimiento</t>
-  </si>
-  <si>
-    <t>Pantalla de consulta de requisitos</t>
-  </si>
-  <si>
-    <t>Interfaz para revisar esta lista de requerimientos</t>
-  </si>
-  <si>
-    <t>Mapa general del proyecto</t>
-  </si>
-  <si>
-    <t>Orden y dependencias entre los documentos de diseño</t>
-  </si>
-  <si>
-    <t>Documentos de diseño por módulo</t>
-  </si>
-  <si>
-    <t>Diseños detallados de cada sección del sistema</t>
-  </si>
-  <si>
-    <t>Documentos de diseño archivados</t>
-  </si>
-  <si>
-    <t>Diseños de funcionalidades ya terminadas</t>
-  </si>
-  <si>
-    <t>Guías del proyecto</t>
-  </si>
-  <si>
-    <t>Decisiones sobre seguridad, roles y estructura general</t>
-  </si>
-  <si>
     <t>SED — WBS del Proyecto</t>
   </si>
   <si>
-    <t>Resumen Ejecutivo</t>
-  </si>
-  <si>
-    <t>Tareas</t>
-  </si>
-  <si>
-    <t>Estimación</t>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>Dependencias</t>
   </si>
   <si>
     <t>Horas</t>
   </si>
   <si>
-    <t>Estado</t>
-  </si>
-  <si>
-    <t>Dependencias principales</t>
-  </si>
-  <si>
-    <t>1. Shell de la aplicación</t>
-  </si>
-  <si>
-    <t>40h</t>
-  </si>
-  <si>
-    <t>19h</t>
-  </si>
-  <si>
-    <t>✅ Completado</t>
-  </si>
-  <si>
-    <t>Ninguna (punto de partida)</t>
-  </si>
-  <si>
-    <t>2. Metas — Asignación de inicio de año</t>
-  </si>
-  <si>
-    <t>48h</t>
+    <t>Comentarios</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Shell de la Aplicación</t>
+  </si>
+  <si>
+    <t>Configuración inicial del entorno</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>6h</t>
+  </si>
+  <si>
+    <t>Incluye framework de interfaz, sistema de estilos base y estructura de carpetas.</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Vistas y rutas dinámicas según el menú</t>
+  </si>
+  <si>
+    <t>3.5h</t>
+  </si>
+  <si>
+    <t>Cada opción del menú lleva a una pantalla. Las rutas se generan automáticamente según el perfil.</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>Esqueleto de secciones y menú</t>
+  </si>
+  <si>
+    <t>2.5h</t>
+  </si>
+  <si>
+    <t>Pantalla principal con menú lateral, encabezado y área de contenido.</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>Agregar autenticación interna y externa</t>
+  </si>
+  <si>
+    <t>Login simulado para pruebas. Preparado para conectar con SSO empresarial.</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Centralizar estilos y colores</t>
+  </si>
+  <si>
+    <t>1.5h</t>
+  </si>
+  <si>
+    <t>Paleta de colores, tipografía y bordes definidos. Tema claro y oscuro.</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>Definición de pantallas principales</t>
+  </si>
+  <si>
+    <t>1h</t>
+  </si>
+  <si>
+    <t>Bocetos iniciales de las 10 secciones del sistema.</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>Instalación de dependencias SDD</t>
+  </si>
+  <si>
+    <t>Herramientas de validación y control de calidad del código.</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>Definición de secciones y orden</t>
+  </si>
+  <si>
+    <t>Orden del menú y agrupación de pantallas por módulo.</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Sección de inicio de año</t>
   </si>
   <si>
     <t>4.5h</t>
   </si>
   <si>
-    <t>Sección 1</t>
-  </si>
-  <si>
-    <t>3. Metas — Avance de medio año</t>
-  </si>
-  <si>
-    <t>16h</t>
-  </si>
-  <si>
-    <t>6h</t>
-  </si>
-  <si>
-    <t>Sección 2</t>
-  </si>
-  <si>
-    <t>4. Mi evaluación — Autoevaluación fin de año</t>
-  </si>
-  <si>
-    <t>32h</t>
-  </si>
-  <si>
-    <t>7h</t>
-  </si>
-  <si>
-    <t>Secciones 2, 3, 5</t>
-  </si>
-  <si>
-    <t>5. Administración RH — Competencias</t>
-  </si>
-  <si>
-    <t>36h</t>
-  </si>
-  <si>
-    <t>2.5h</t>
-  </si>
-  <si>
-    <t>6. Evaluación RH — Fin de año</t>
+    <t>Pantalla completa: crear categorías, agregar metas, validar ponderación 100%, vista de solo lectura para jefes.</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Sección de gráficos avance y resultados</t>
+  </si>
+  <si>
+    <t>Barras de progreso y semáforos por meta y por categoría.</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Sección de medio año</t>
+  </si>
+  <si>
+    <t>Edición de metas existentes. No permite eliminar, solo ajustar valores.</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>Sección de fin de año</t>
+  </si>
+  <si>
+    <t>2.1, 3.1</t>
+  </si>
+  <si>
+    <t>3h</t>
+  </si>
+  <si>
+    <t>Autoevaluación de competencias (escala 1-5) y cierre de metas con valor final.</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>Realizar ajustes en pantallas evaluación</t>
+  </si>
+  <si>
+    <t>Correcciones de formato, validaciones y experiencia de usuario.</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>Agregar botón y calificación inversa</t>
+  </si>
+  <si>
+    <t>Flujo donde el colaborador elige metas con objetivos a la baja.</t>
+  </si>
+  <si>
+    <t>5.1</t>
+  </si>
+  <si>
+    <t>Sección admin de RH</t>
+  </si>
+  <si>
+    <t>Administración de pilares y competencias. Catálogo único para toda la empresa.</t>
+  </si>
+  <si>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>Listado de empleados con estado de evaluación</t>
+  </si>
+  <si>
+    <t>4.1, 5.1</t>
+  </si>
+  <si>
+    <t>Tabla con filtro por nombre, perfil y estado. Incluye barra de búsqueda.</t>
+  </si>
+  <si>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>Comparación autoevaluación vs evaluación RH</t>
+  </si>
+  <si>
+    <t>2h</t>
+  </si>
+  <si>
+    <t>Vista lado a lado para detectar diferencias entre la autoevaluación y la evaluación formal.</t>
+  </si>
+  <si>
+    <t>7.1</t>
+  </si>
+  <si>
+    <t>Sección evaluación de jefes/usuario</t>
+  </si>
+  <si>
+    <t>Cuadrícula interactiva para ubicar colaboradores por desempeño y potencial.</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>Sección jerarquía de áreas</t>
+  </si>
+  <si>
+    <t>Árbol organizacional con dos vistas: corporativa y retail.</t>
+  </si>
+  <si>
+    <t>7.3</t>
+  </si>
+  <si>
+    <t>Ajustar gráfico NineBox</t>
+  </si>
+  <si>
+    <t>Grilla 9×9 visualización de puntuaciones.</t>
+  </si>
+  <si>
+    <t>8.1</t>
+  </si>
+  <si>
+    <t>Sección y opciones de reportes</t>
+  </si>
+  <si>
+    <t>1.2, 2.1, 3.1</t>
+  </si>
+  <si>
+    <t>Lista de colaboradores a cargo con acceso directo a sus metas y evaluaciones.</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>Página de perfil con datos y actividad</t>
+  </si>
+  <si>
+    <t>Muestra nombre, correo, historial de actividad reciente y botón de cerrar sesión.</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>Backend — Infraestructura</t>
+  </si>
+  <si>
+    <t>Configurar APIs y persistencia de datos</t>
   </si>
   <si>
     <t>5h</t>
   </si>
   <si>
-    <t>Secciones 4, 5</t>
-  </si>
-  <si>
-    <t>7. Matriz 9×9 — Evaluación de jefes</t>
-  </si>
-  <si>
-    <t>28h</t>
-  </si>
-  <si>
-    <t>7.5h</t>
-  </si>
-  <si>
-    <t>Secciones 1, 4</t>
-  </si>
-  <si>
-    <t>8. Mis evaluados</t>
+    <t>Servidor que conecta el sistema con la base de datos. Guarda y consulta información.</t>
+  </si>
+  <si>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t>Reemplazar datos mockup por api</t>
+  </si>
+  <si>
+    <t>4h</t>
+  </si>
+  <si>
+    <t>Sustituir datos de prueba por datos reales del servidor progresivamente.</t>
+  </si>
+  <si>
+    <t>10.3</t>
+  </si>
+  <si>
+    <t>Configurar y ajustar pruebas de api y datos</t>
+  </si>
+  <si>
+    <t>Pruebas automáticas que verifican que los procesos responden correctamente.</t>
+  </si>
+  <si>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>Pruebas de flujo completo</t>
+  </si>
+  <si>
+    <t>Recorrido completo de principio a fin: login, crear meta, evaluar, cerrar ciclo.</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>Módulo de base de datos</t>
+  </si>
+  <si>
+    <t>Estructura de tablas, relaciones y reglas de información.</t>
+  </si>
+  <si>
+    <t>10.6</t>
+  </si>
+  <si>
+    <t>Pruebas generales de cambios SED</t>
+  </si>
+  <si>
+    <t>Verificación de que los cambios no rompan funcionalidad existente.</t>
+  </si>
+  <si>
+    <t>10.7</t>
+  </si>
+  <si>
+    <t>Revisar comentarios y feedback</t>
+  </si>
+  <si>
+    <t>Ajustes derivados de revisiones de calidad del código.</t>
+  </si>
+  <si>
+    <t>10.8</t>
+  </si>
+  <si>
+    <t>Desplegar prototipo dev en UAT</t>
+  </si>
+  <si>
+    <t>Publicar el sistema en ambiente de pruebas para validación.</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>Pruebas y desplieegue</t>
+  </si>
+  <si>
+    <t>Pruebas de usuario (UAT)</t>
+  </si>
+  <si>
+    <t>20h</t>
+  </si>
+  <si>
+    <t>4-6 sesiones con usuarios reales (RH, jefes, colaboradores). Validar flujos completos: metas, avance, autoevaluación, evaluación RH, matriz 9×9. Incluye preparación y reporte de incidencias.</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>Ajustes post-pruebas</t>
   </si>
   <si>
     <t>8h</t>
   </si>
   <si>
-    <t>3h</t>
-  </si>
-  <si>
-    <t>Secciones 1, 2, 3</t>
-  </si>
-  <si>
-    <t>9. Perfil de usuario</t>
-  </si>
-  <si>
-    <t>10. Backend — Infraestructura</t>
-  </si>
-  <si>
-    <t>56h</t>
-  </si>
-  <si>
-    <t>22.5h</t>
-  </si>
-  <si>
-    <t>Ninguna (paralelo)</t>
-  </si>
-  <si>
-    <t>11. Pendientes finales</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>34h</t>
-  </si>
-  <si>
-    <t>🔲 Pendiente</t>
-  </si>
-  <si>
-    <t>Ver detalle abajo</t>
-  </si>
-  <si>
-    <t>**TOTAL**</t>
-  </si>
-  <si>
-    <t>**33**</t>
-  </si>
-  <si>
-    <t>**112.5h**</t>
-  </si>
-  <si>
-    <t>**28/33 completado**</t>
-  </si>
-  <si>
-    <t>Detalle de Tareas</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Tarea</t>
-  </si>
-  <si>
-    <t>Dependencias</t>
-  </si>
-  <si>
-    <t>Comentarios</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>Shell de la Aplicación</t>
-  </si>
-  <si>
-    <t>Configuración inicial del entorno</t>
-  </si>
-  <si>
-    <t>Incluye framework de interfaz, sistema de estilos base y estructura de carpetas.</t>
-  </si>
-  <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>Vistas y rutas dinámicas según el menú</t>
-  </si>
-  <si>
-    <t>3.5h</t>
-  </si>
-  <si>
-    <t>Cada opción del menú lleva a una pantalla. Las rutas se generan automáticamente según el perfil.</t>
-  </si>
-  <si>
-    <t>1.3</t>
-  </si>
-  <si>
-    <t>Esqueleto de secciones y menú</t>
-  </si>
-  <si>
-    <t>Pantalla principal con menú lateral, encabezado y área de contenido.</t>
-  </si>
-  <si>
-    <t>1.4</t>
-  </si>
-  <si>
-    <t>Agregar autenticación interna y externa</t>
-  </si>
-  <si>
-    <t>Login simulado para pruebas. Preparado para conectar con SSO empresarial.</t>
-  </si>
-  <si>
-    <t>1.5</t>
-  </si>
-  <si>
-    <t>Centralizar estilos y colores</t>
-  </si>
-  <si>
-    <t>1.5h</t>
-  </si>
-  <si>
-    <t>Paleta de colores, tipografía y bordes definidos. Tema claro y oscuro.</t>
-  </si>
-  <si>
-    <t>1.6</t>
-  </si>
-  <si>
-    <t>Definición de pantallas principales</t>
-  </si>
-  <si>
-    <t>1h</t>
-  </si>
-  <si>
-    <t>Bocetos iniciales de las 10 secciones del sistema.</t>
-  </si>
-  <si>
-    <t>1.7</t>
-  </si>
-  <si>
-    <t>Instalación de dependencias SDD</t>
-  </si>
-  <si>
-    <t>Herramientas de validación y control de calidad del código.</t>
-  </si>
-  <si>
-    <t>1.8</t>
-  </si>
-  <si>
-    <t>Definición de secciones y orden</t>
-  </si>
-  <si>
-    <t>Orden del menú y agrupación de pantallas por módulo.</t>
-  </si>
-  <si>
-    <t>2.1</t>
-  </si>
-  <si>
-    <t>Sección de inicio de año</t>
-  </si>
-  <si>
-    <t>Pantalla completa: crear categorías, agregar metas, validar ponderación 100%, vista de solo lectura para jefes.</t>
-  </si>
-  <si>
-    <t>3.1</t>
-  </si>
-  <si>
-    <t>Sección de gráficos avance y resultados</t>
-  </si>
-  <si>
-    <t>Barras de progreso y semáforos por meta y por categoría.</t>
-  </si>
-  <si>
-    <t>3.2</t>
-  </si>
-  <si>
-    <t>Sección de medio año</t>
-  </si>
-  <si>
-    <t>Edición de metas existentes. No permite eliminar, solo ajustar valores.</t>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>Sección de fin de año</t>
-  </si>
-  <si>
-    <t>2.1, 3.1</t>
-  </si>
-  <si>
-    <t>Autoevaluación de competencias (escala 1-5) y cierre de metas con valor final.</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>Realizar ajustes en pantallas evaluación</t>
-  </si>
-  <si>
-    <t>Correcciones de formato, validaciones y experiencia de usuario.</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>Agregar botón y calificación inversa</t>
-  </si>
-  <si>
-    <t>Flujo donde el colaborador elige metas con objetivos a la baja.</t>
-  </si>
-  <si>
-    <t>5.1</t>
-  </si>
-  <si>
-    <t>Sección admin de RH</t>
-  </si>
-  <si>
-    <t>Administración de pilares y competencias. Catálogo único para toda la empresa.</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>Listado de empleados con estado de evaluación</t>
-  </si>
-  <si>
-    <t>4.1, 5.1</t>
-  </si>
-  <si>
-    <t>Tabla con filtro por nombre, perfil y estado. Incluye barra de búsqueda.</t>
-  </si>
-  <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>Comparación autoevaluación vs evaluación RH</t>
-  </si>
-  <si>
-    <t>2h</t>
-  </si>
-  <si>
-    <t>Vista lado a lado para detectar diferencias entre la autoevaluación y la evaluación formal.</t>
-  </si>
-  <si>
-    <t>7.1</t>
-  </si>
-  <si>
-    <t>Sección evaluación de jefes/usuario</t>
-  </si>
-  <si>
-    <t>Cuadrícula interactiva para ubicar colaboradores por desempeño y potencial.</t>
-  </si>
-  <si>
-    <t>7.2</t>
-  </si>
-  <si>
-    <t>Sección jerarquía de áreas</t>
-  </si>
-  <si>
-    <t>Árbol organizacional con dos vistas: corporativa y retail.</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>Ajustar gráfico NineBox</t>
-  </si>
-  <si>
-    <t>Grilla 9×9 visualización de puntuaciones.</t>
-  </si>
-  <si>
-    <t>8.1</t>
-  </si>
-  <si>
-    <t>Sección y opciones de reportes</t>
-  </si>
-  <si>
-    <t>1.2, 2.1, 3.1</t>
-  </si>
-  <si>
-    <t>Lista de colaboradores a cargo con acceso directo a sus metas y evaluaciones.</t>
-  </si>
-  <si>
-    <t>9.1</t>
-  </si>
-  <si>
-    <t>Página de perfil con datos y actividad</t>
-  </si>
-  <si>
-    <t>Muestra nombre, correo, historial de actividad reciente y botón de cerrar sesión.</t>
-  </si>
-  <si>
-    <t>10.1</t>
-  </si>
-  <si>
-    <t>Backend — Infraestructura</t>
-  </si>
-  <si>
-    <t>Configurar APIs y persistencia de datos</t>
-  </si>
-  <si>
-    <t>Servidor que conecta el sistema con la base de datos. Guarda y consulta información.</t>
-  </si>
-  <si>
-    <t>10.2</t>
-  </si>
-  <si>
-    <t>Reemplazar datos mockup por api</t>
-  </si>
-  <si>
-    <t>4h</t>
-  </si>
-  <si>
-    <t>Sustituir datos de prueba por datos reales del servidor progresivamente.</t>
-  </si>
-  <si>
-    <t>10.3</t>
-  </si>
-  <si>
-    <t>Configurar y ajustar pruebas de api y datos</t>
-  </si>
-  <si>
-    <t>Pruebas automáticas que verifican que los procesos responden correctamente.</t>
-  </si>
-  <si>
-    <t>10.4</t>
-  </si>
-  <si>
-    <t>Pruebas de flujo completo</t>
-  </si>
-  <si>
-    <t>Recorrido completo de principio a fin: login, crear meta, evaluar, cerrar ciclo.</t>
-  </si>
-  <si>
-    <t>10.5</t>
-  </si>
-  <si>
-    <t>Módulo de base de datos</t>
-  </si>
-  <si>
-    <t>Estructura de tablas, relaciones y reglas de información.</t>
-  </si>
-  <si>
-    <t>10.6</t>
-  </si>
-  <si>
-    <t>Pruebas generales de cambios SED</t>
-  </si>
-  <si>
-    <t>Verificación de que los cambios no rompan funcionalidad existente.</t>
-  </si>
-  <si>
-    <t>10.7</t>
-  </si>
-  <si>
-    <t>Revisar comentarios y feedback</t>
-  </si>
-  <si>
-    <t>Ajustes derivados de revisiones de calidad del código.</t>
-  </si>
-  <si>
-    <t>10.8</t>
-  </si>
-  <si>
-    <t>Desplegar prototipo dev en UAT</t>
-  </si>
-  <si>
-    <t>Publicar el sistema en ambiente de pruebas para validación.</t>
-  </si>
-  <si>
-    <t>11.1</t>
-  </si>
-  <si>
-    <t>Pendientes Finales</t>
-  </si>
-  <si>
-    <t>Pruebas de usuario (UAT)</t>
-  </si>
-  <si>
-    <t>20h</t>
-  </si>
-  <si>
-    <t>4-6 sesiones con usuarios reales (RH, jefes, colaboradores). Validar flujos completos: metas, avance, autoevaluación, evaluación RH, matriz 9×9. Incluye preparación y reporte de incidencias.</t>
-  </si>
-  <si>
-    <t>11.2</t>
-  </si>
-  <si>
-    <t>Ajustes post-pruebas</t>
-  </si>
-  <si>
     <t>Corrección de incidencias priorizadas: bloqueadores (flujo roto), mayores (funcionalidad incorrecta), menores (mejoras visuales).</t>
   </si>
   <si>
@@ -1062,13 +867,16 @@
   </si>
   <si>
     <t>Migración a producción: credenciales, certificados, dominio. Verificación post-despliegue. Monitoreo de estabilidad las primeras 48h. Plan de retroceso documentado.</t>
+  </si>
+  <si>
+    <t>El jefe puede ver gráfico de radar y tabla de competencias. No puede calificar (esa tarea es de RH)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1092,14 +900,8 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF2F5496"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1110,12 +912,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5496"/>
         <bgColor rgb="FF2F5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6E4F0"/>
-        <bgColor rgb="FFD6E4F0"/>
       </patternFill>
     </fill>
   </fills>
@@ -1146,15 +942,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1461,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1474,15 +1267,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1622,7 +1415,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>37</v>
       </c>
@@ -1668,7 +1461,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>48</v>
       </c>
@@ -1691,7 +1484,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>54</v>
       </c>
@@ -1768,7 +1561,7 @@
         <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>71</v>
@@ -1829,7 +1622,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>86</v>
       </c>
@@ -2013,7 +1806,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>130</v>
       </c>
@@ -2059,7 +1852,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
@@ -2102,159 +1895,31 @@
         <v>149</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="B30" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="69" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-    </row>
-    <row r="33" spans="1:7" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-    </row>
-    <row r="34" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-    </row>
-    <row r="35" spans="1:7" ht="69" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-    </row>
-    <row r="36" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-    </row>
-    <row r="37" spans="1:7" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-    </row>
-    <row r="38" spans="1:7" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2266,10 +1931,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.21875" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
@@ -2278,971 +1943,693 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-    </row>
-    <row r="3" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
+      <c r="A1" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="B9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F4" s="1" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="B10" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="2" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="B11" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="B12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="13" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F8" s="2" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="B15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D9" s="2" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="69" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="69" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="2" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="B17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+    <row r="18" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="B18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F12" s="2" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="B19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="69" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="2" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="B20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="E20" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>237</v>
+        <v>125</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>237</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E24" s="2" t="s">
+    </row>
+    <row r="29" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" s="2" t="s">
+    </row>
+    <row r="30" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="B31" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C28" s="2" t="s">
+      <c r="B33" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F28" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="D34" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="35" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F30" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="D35" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>125</v>
+        <v>271</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>346</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
